--- a/AutoXP3_samples_split/Sample9.xlsx
+++ b/AutoXP3_samples_split/Sample9.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Definition" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,19 +11,26 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
-      <name val="Calibri"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="128"/>
+      <family val="3"/>
+      <sz val="6"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -48,11 +54,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="1" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -416,7 +423,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -478,7 +485,6 @@
       <c r="F2" t="n">
         <v>1</v>
       </c>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -503,7 +509,6 @@
       <c r="F3" t="n">
         <v>1</v>
       </c>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -528,7 +533,6 @@
       <c r="F4" t="n">
         <v>1</v>
       </c>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -556,8 +560,6 @@
           <t>categorical</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -565,18 +567,15 @@
           <t>Y1</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6">
-        <f>5</f>
-        <v/>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -590,8 +589,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -630,21 +629,21 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.1202986361416724</v>
+        <v>7.7745</v>
       </c>
     </row>
     <row r="3">
@@ -652,21 +651,21 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>5.79</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>3.91</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>6.04</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>-3.625212336542168</v>
+        <v>13.6743</v>
       </c>
     </row>
     <row r="4">
@@ -674,21 +673,21 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>7.3</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>1.82</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>7.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>-20.99088696973254</v>
+        <v>6.7398</v>
       </c>
     </row>
     <row r="5">
@@ -696,13 +695,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>3.99</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>7.91</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>1.93</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -710,7 +709,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>-57.02975246721328</v>
+        <v>1.2499</v>
       </c>
     </row>
     <row r="6">
@@ -718,21 +717,21 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>7.02</v>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>3.55</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>2.85</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>-12.55939991225033</v>
+        <v>6.3055</v>
       </c>
     </row>
     <row r="7">
@@ -740,13 +739,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>6.54</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>3.33</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -754,7 +753,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>7.903967955917133</v>
+        <v>9.271800000000001</v>
       </c>
     </row>
     <row r="8">
@@ -762,13 +761,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>7.87</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>7.39</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>4.53</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -776,7 +775,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>-12.91166829147347</v>
+        <v>21.1141</v>
       </c>
     </row>
     <row r="9">
@@ -784,21 +783,21 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>4.18</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>5.23</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>4.98</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.258770287934129</v>
+        <v>14.4592</v>
       </c>
     </row>
     <row r="10">
@@ -806,21 +805,21 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>3.8</v>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>7.64</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>4.26</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>-16.05988241304139</v>
+        <v>17.3331</v>
       </c>
     </row>
     <row r="11">
@@ -828,13 +827,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>5.49</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>5.88</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -842,227 +841,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>-54.52787283938813</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>2.001454602083955</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" t="n">
-        <v>3</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>-1.984248517166124</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="n">
-        <v>2</v>
-      </c>
-      <c r="C14" t="n">
-        <v>4</v>
-      </c>
-      <c r="D14" t="n">
-        <v>6</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>-24.95963150352441</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="n">
-        <v>3</v>
-      </c>
-      <c r="C15" t="n">
-        <v>6</v>
-      </c>
-      <c r="D15" t="n">
-        <v>9</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>-54.80470594051101</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="n">
-        <v>4</v>
-      </c>
-      <c r="C16" t="n">
-        <v>8</v>
-      </c>
-      <c r="D16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>-10.52025768381318</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="n">
-        <v>5</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>5</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>3.943422120524641</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="n">
-        <v>6</v>
-      </c>
-      <c r="C18" t="n">
-        <v>2</v>
-      </c>
-      <c r="D18" t="n">
-        <v>8</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>-10.70736067750986</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="n">
-        <v>7</v>
-      </c>
-      <c r="C19" t="n">
-        <v>4</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>5.335330626077367</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="n">
-        <v>8</v>
-      </c>
-      <c r="C20" t="n">
-        <v>6</v>
-      </c>
-      <c r="D20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>-19.83260717520187</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="n">
-        <v>9</v>
-      </c>
-      <c r="C21" t="n">
-        <v>8</v>
-      </c>
-      <c r="D21" t="n">
-        <v>7</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>-52.53223015756102</v>
+        <v>22.0442</v>
       </c>
     </row>
   </sheetData>
@@ -1077,7 +856,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1099,7 +878,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Y1 = 0.8*X1 - 1.1*(X2*X3) + categorical effect</t>
+          <t>Y1 = 0.8*X1 - 2.0*X2 - 1.5*X3 + 1.1*(X2*X3) + cat(A=0,B=2,C=4)</t>
         </is>
       </c>
     </row>
@@ -1111,7 +890,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Small X2 and X3 help; category C raises Y1</t>
+          <t>X1=10,X2=10,X3=10,X4=C (max Y1=87)</t>
         </is>
       </c>
     </row>
